--- a/shift_report_forms/020_dispatch_availability_survey--shift_report_forms.xlsx
+++ b/shift_report_forms/020_dispatch_availability_survey--shift_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>availability_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dispatcher Availability</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>availability_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shift Preferences</t>
+          <t>Preferred Work Time</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>scheduling_constraints_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,45 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>dispatchers_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dispatchers</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter names of dispatchers</t>
-        </is>
-      </c>
+          <t>Dispatchers I Report To</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>breaks_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>Breaks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>availability_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>Available Days</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,46 +658,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>available_times_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Select days available</t>
-        </is>
-      </c>
+          <t>Available Times</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Select times</t>
-        </is>
-      </c>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -711,27 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>available_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Select breaks</t>
-        </is>
-      </c>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -743,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>notes_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -769,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,204 +781,850 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>availability_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>availability_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>06:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>07:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>08:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>660</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>720</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>720</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>780</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>780</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>840</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>900</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>availability_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dispatchers_1_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dispatchers_1_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>second</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dispatchers_1_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>dispatchers_1_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>saturday</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>availability_3_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sunday</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>available_times_1_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>available_1_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>available_1_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
